--- a/CRMGUIFrameWork2/testdata/testScriptData.xlsx
+++ b/CRMGUIFrameWork2/testdata/testScriptData.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SeleniumTekPyramid\CRMGUIFrameWork\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\AutomationTL\CRMGUIFrameWork2\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBFC6E43-4B17-40EA-AB41-EC5EAC95DBC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{446A2795-1660-437F-A092-0E8BC1E50B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="org" sheetId="1" r:id="rId1"/>
+    <sheet name="contact" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="26">
   <si>
     <t>TC_ID</t>
   </si>
@@ -73,6 +74,36 @@
   </si>
   <si>
     <t>9876543211</t>
+  </si>
+  <si>
+    <t>tc_02</t>
+  </si>
+  <si>
+    <t>tc_03</t>
+  </si>
+  <si>
+    <t>tc_04</t>
+  </si>
+  <si>
+    <t>tc_05</t>
+  </si>
+  <si>
+    <t>tc_06</t>
+  </si>
+  <si>
+    <t>CreateContactTest</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>Chinnu_</t>
+  </si>
+  <si>
+    <t>OrgName</t>
+  </si>
+  <si>
+    <t>Rolex_</t>
   </si>
 </sst>
 </file>
@@ -457,7 +488,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
@@ -494,7 +525,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
@@ -508,6 +539,103 @@
       <c r="E8" s="2" t="s">
         <v>15</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6686EEB-5019-4027-9B6F-BAA3428B23B2}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
